--- a/web/files/九龙-启德-The Henley III.xlsx
+++ b/web/files/九龙-启德-The Henley III.xlsx
@@ -19751,18 +19751,18 @@
       </c>
       <c r="J300" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K300" s="5" t="n">
-        <v>21008400</v>
+        <v>24723300</v>
       </c>
       <c r="L300" s="5" t="n">
-        <v>27003</v>
+        <v>31778</v>
       </c>
       <c r="M300" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N300" s="3" t="inlineStr">
@@ -20123,18 +20123,18 @@
       </c>
       <c r="J306" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K306" s="5" t="n">
-        <v>20946080</v>
+        <v>24649960</v>
       </c>
       <c r="L306" s="5" t="n">
-        <v>26923</v>
+        <v>31684</v>
       </c>
       <c r="M306" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N306" s="3" t="inlineStr">
@@ -20495,18 +20495,18 @@
       </c>
       <c r="J312" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K312" s="5" t="n">
-        <v>20882940</v>
+        <v>24575655</v>
       </c>
       <c r="L312" s="5" t="n">
-        <v>26842</v>
+        <v>31588</v>
       </c>
       <c r="M312" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N312" s="3" t="inlineStr">
@@ -20805,18 +20805,18 @@
       </c>
       <c r="J317" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K317" s="5" t="n">
-        <v>14887920</v>
+        <v>17520540</v>
       </c>
       <c r="L317" s="5" t="n">
-        <v>27570</v>
+        <v>32445</v>
       </c>
       <c r="M317" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N317" s="3" t="inlineStr">
@@ -20867,18 +20867,18 @@
       </c>
       <c r="J318" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K318" s="5" t="n">
-        <v>20819800</v>
+        <v>24501350</v>
       </c>
       <c r="L318" s="5" t="n">
-        <v>26761</v>
+        <v>31493</v>
       </c>
       <c r="M318" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N318" s="3" t="inlineStr">
@@ -21549,18 +21549,18 @@
       </c>
       <c r="J329" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K329" s="5" t="n">
-        <v>14842820</v>
+        <v>17467465</v>
       </c>
       <c r="L329" s="5" t="n">
-        <v>27487</v>
+        <v>32347</v>
       </c>
       <c r="M329" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N329" s="3" t="inlineStr">
@@ -21611,18 +21611,18 @@
       </c>
       <c r="J330" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K330" s="5" t="n">
-        <v>20756660</v>
+        <v>24427045</v>
       </c>
       <c r="L330" s="5" t="n">
-        <v>26680</v>
+        <v>31397</v>
       </c>
       <c r="M330" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N330" s="3" t="inlineStr">
@@ -22665,18 +22665,18 @@
       </c>
       <c r="J347" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K347" s="5" t="n">
-        <v>14708340</v>
+        <v>17309205</v>
       </c>
       <c r="L347" s="5" t="n">
-        <v>27238</v>
+        <v>32054</v>
       </c>
       <c r="M347" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N347" s="3" t="inlineStr">
@@ -23037,18 +23037,18 @@
       </c>
       <c r="J353" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K353" s="5" t="n">
-        <v>14663240</v>
+        <v>17256130</v>
       </c>
       <c r="L353" s="5" t="n">
-        <v>27154</v>
+        <v>31956</v>
       </c>
       <c r="M353" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N353" s="3" t="inlineStr">

--- a/web/files/九龙-启德-The Henley III.xlsx
+++ b/web/files/九龙-启德-The Henley III.xlsx
@@ -790,7 +790,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -852,7 +852,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
+          <t>2022-08-26</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2021-10-10</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2021-10-10</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
+          <t>2022-05-26</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -3055,42 +3055,34 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>25996000</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>33543</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K38" s="5" t="n">
+        <v>25996000</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>33543</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
@@ -3099,7 +3091,7 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3126,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3196,7 +3188,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3258,7 +3250,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3320,7 +3312,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3452,7 +3444,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3514,7 +3506,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
+          <t>2022-05-26</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3576,7 +3568,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2022-05-27</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3638,7 +3630,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3700,7 +3692,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3902,7 +3894,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3964,7 +3956,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -4026,7 +4018,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4088,7 +4080,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4290,7 +4282,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2021-11-14</t>
+          <t>2021-11-15</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4352,7 +4344,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2022-04-25</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4414,7 +4406,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4476,7 +4468,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4678,7 +4670,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2022-01-30</t>
+          <t>2022-01-31</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4740,7 +4732,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4802,7 +4794,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4864,7 +4856,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4996,7 +4988,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -5058,7 +5050,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2022-01-11</t>
+          <t>2022-01-12</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -5120,7 +5112,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5182,7 +5174,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5244,7 +5236,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5446,7 +5438,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2021-11-02</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5508,7 +5500,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2022-01-25</t>
+          <t>2022-01-26</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5570,7 +5562,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5632,7 +5624,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5834,7 +5826,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2021-11-02</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5896,7 +5888,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5958,7 +5950,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -6020,7 +6012,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -6222,7 +6214,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2021-11-08</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6284,7 +6276,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6346,7 +6338,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2021-10-10</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6408,7 +6400,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6610,7 +6602,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6672,7 +6664,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6734,7 +6726,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2022-02-15</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6796,7 +6788,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2022-10-25</t>
+          <t>2022-10-26</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6928,7 +6920,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6990,7 +6982,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -7052,7 +7044,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -7114,7 +7106,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2022-02-14</t>
+          <t>2022-02-15</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -7176,7 +7168,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2023-02-02</t>
+          <t>2023-02-03</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7378,7 +7370,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2021-10-10</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7440,7 +7432,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2021-09-26</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7502,7 +7494,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2022-01-02</t>
+          <t>2022-01-03</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7564,7 +7556,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7766,7 +7758,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7828,7 +7820,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2021-09-29</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7890,7 +7882,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2022-01-20</t>
+          <t>2022-01-21</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7952,7 +7944,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -8154,7 +8146,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -8216,7 +8208,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8278,7 +8270,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8340,7 +8332,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2023-01-16</t>
+          <t>2023-01-17</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8542,7 +8534,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2021-10-18</t>
+          <t>2021-10-19</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8604,7 +8596,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2021-09-26</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8666,7 +8658,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8728,7 +8720,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8930,7 +8922,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2021-10-10</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8992,7 +8984,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -9054,7 +9046,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2021-10-24</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -9116,7 +9108,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2023-03-09</t>
+          <t>2023-03-10</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -9318,7 +9310,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9380,7 +9372,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9442,7 +9434,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2022-01-05</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9504,7 +9496,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2022-10-18</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9706,7 +9698,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2021-10-19</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9768,7 +9760,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2021-09-26</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9830,7 +9822,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2022-01-26</t>
+          <t>2022-01-27</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9892,7 +9884,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2022-02-10</t>
+          <t>2022-02-11</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -10094,7 +10086,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2021-10-10</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -10156,7 +10148,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
+          <t>2021-09-04</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -10218,7 +10210,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2021-10-04</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -10280,7 +10272,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2022-04-13</t>
+          <t>2022-04-14</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -10482,7 +10474,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10544,7 +10536,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
+          <t>2021-09-04</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10606,7 +10598,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
+          <t>2021-10-04</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10668,7 +10660,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10870,7 +10862,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2022-01-05</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10932,7 +10924,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10994,7 +10986,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2021-10-07</t>
+          <t>2021-10-08</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -11056,7 +11048,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2021-10-04</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -11258,7 +11250,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2021-12-13</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -11320,7 +11312,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2022-05-22</t>
+          <t>2022-05-23</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -11382,7 +11374,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2022-01-16</t>
+          <t>2022-01-17</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11444,7 +11436,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2021-09-29</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11646,7 +11638,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2022-01-13</t>
+          <t>2022-01-14</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11708,7 +11700,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2022-05-22</t>
+          <t>2022-05-23</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11770,7 +11762,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2022-01-23</t>
+          <t>2022-01-24</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11832,7 +11824,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -12034,7 +12026,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2022-03-31</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -12096,7 +12088,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2023-03-09</t>
+          <t>2023-03-10</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -12158,7 +12150,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -12220,7 +12212,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -12422,7 +12414,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2021-11-15</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12484,7 +12476,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12546,7 +12538,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12608,7 +12600,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2021-10-07</t>
+          <t>2021-10-08</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -12810,7 +12802,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2021-12-14</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12872,7 +12864,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12934,7 +12926,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -12996,7 +12988,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -13198,7 +13190,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2022-02-09</t>
+          <t>2022-02-10</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -13260,7 +13252,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -13322,7 +13314,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -13384,7 +13376,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2022-01-05</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -13586,7 +13578,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2022-03-06</t>
+          <t>2022-03-07</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13648,7 +13640,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13710,7 +13702,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13772,7 +13764,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2022-08-28</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -13896,7 +13888,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -14222,7 +14214,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2022-01-13</t>
+          <t>2022-01-14</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -14284,7 +14276,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -14346,7 +14338,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -14408,7 +14400,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2021-09-26</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -14532,7 +14524,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14594,7 +14586,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -14656,7 +14648,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -14718,7 +14710,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2021-09-26</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -14780,7 +14772,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -14904,7 +14896,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2022-03-06</t>
+          <t>2022-03-07</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -14966,7 +14958,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -15028,7 +15020,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -15090,7 +15082,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -15152,7 +15144,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2021-12-09</t>
+          <t>2021-12-10</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -15276,7 +15268,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2023-01-25</t>
+          <t>2023-01-26</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -15338,7 +15330,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -15400,7 +15392,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -15462,7 +15454,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -15524,7 +15516,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2021-12-07</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -15586,7 +15578,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -15648,7 +15640,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2022-06-12</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -15710,7 +15702,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -15772,7 +15764,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -15834,7 +15826,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -15896,7 +15888,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2022-01-03</t>
+          <t>2022-01-04</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -16020,7 +16012,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2021-10-11</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -16082,7 +16074,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2022-08-10</t>
+          <t>2022-08-11</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -16144,7 +16136,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -16206,7 +16198,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -16268,7 +16260,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2021-12-19</t>
+          <t>2021-12-20</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -16392,7 +16384,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -16454,7 +16446,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2022-06-05</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -16516,7 +16508,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -16578,7 +16570,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -16640,7 +16632,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2021-12-19</t>
+          <t>2021-12-20</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -16702,7 +16694,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2022-02-10</t>
+          <t>2022-02-11</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -16764,7 +16756,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2021-09-26</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -16826,7 +16818,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
+          <t>2022-05-26</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -16888,7 +16880,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -16950,7 +16942,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -17012,7 +17004,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2021-09-26</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -17074,7 +17066,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2021-10-17</t>
+          <t>2021-10-18</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -17136,7 +17128,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -17198,7 +17190,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
+          <t>2022-05-26</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -17260,7 +17252,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-05-18</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -17322,7 +17314,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -17384,7 +17376,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2021-09-26</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -17446,7 +17438,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2021-10-10</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -17508,7 +17500,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -17570,7 +17562,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2022-05-11</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -17632,7 +17624,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -17694,7 +17686,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -17756,7 +17748,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2021-12-02</t>
+          <t>2021-12-03</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -17818,7 +17810,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2021-09-26</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -17880,7 +17872,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -17942,7 +17934,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2021-12-27</t>
+          <t>2021-12-28</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -18004,7 +17996,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2022-04-25</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -18066,7 +18058,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2021-09-26</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -18128,7 +18120,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2021-09-26</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -18190,7 +18182,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2021-09-26</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -18252,7 +18244,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -18314,7 +18306,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2021-12-10</t>
+          <t>2021-12-11</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -18376,7 +18368,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -18438,7 +18430,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2021-09-26</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -18500,7 +18492,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2021-09-26</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -18562,7 +18554,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -18686,7 +18678,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2022-02-08</t>
+          <t>2022-02-09</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -18748,7 +18740,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -18810,7 +18802,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2021-09-26</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -18872,7 +18864,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2021-09-26</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -18934,7 +18926,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2021-09-26</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -18996,7 +18988,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -19058,7 +19050,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2022-02-08</t>
+          <t>2022-02-09</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -19120,7 +19112,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2022-05-02</t>
+          <t>2022-05-03</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -19182,7 +19174,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
+          <t>2021-11-18</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -19244,7 +19236,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -19306,7 +19298,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2022-01-10</t>
+          <t>2022-01-11</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -19430,7 +19422,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2022-01-09</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -19492,7 +19484,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -19554,7 +19546,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -19616,7 +19608,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -19678,7 +19670,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2022-07-31</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -19751,18 +19743,18 @@
       </c>
       <c r="J300" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K300" s="5" t="n">
-        <v>24723300</v>
+        <v>21008400</v>
       </c>
       <c r="L300" s="5" t="n">
-        <v>31778</v>
+        <v>27003</v>
       </c>
       <c r="M300" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N300" s="3" t="inlineStr">
@@ -19802,7 +19794,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2022-01-09</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -19864,7 +19856,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -19926,7 +19918,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -19988,7 +19980,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -20123,18 +20115,18 @@
       </c>
       <c r="J306" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K306" s="5" t="n">
-        <v>24649960</v>
+        <v>20946080</v>
       </c>
       <c r="L306" s="5" t="n">
-        <v>31684</v>
+        <v>26923</v>
       </c>
       <c r="M306" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N306" s="3" t="inlineStr">
@@ -20174,7 +20166,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2022-01-06</t>
+          <t>2022-01-07</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -20236,7 +20228,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -20298,7 +20290,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -20360,7 +20352,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -20422,7 +20414,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -20495,18 +20487,18 @@
       </c>
       <c r="J312" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K312" s="5" t="n">
-        <v>24575655</v>
+        <v>20882940</v>
       </c>
       <c r="L312" s="5" t="n">
-        <v>31588</v>
+        <v>26842</v>
       </c>
       <c r="M312" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N312" s="3" t="inlineStr">
@@ -20546,7 +20538,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2022-01-02</t>
+          <t>2022-01-03</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
@@ -20608,7 +20600,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -20670,7 +20662,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -20732,7 +20724,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -20805,18 +20797,18 @@
       </c>
       <c r="J317" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K317" s="5" t="n">
-        <v>17520540</v>
+        <v>14887920</v>
       </c>
       <c r="L317" s="5" t="n">
-        <v>32445</v>
+        <v>27570</v>
       </c>
       <c r="M317" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N317" s="3" t="inlineStr">
@@ -20867,18 +20859,18 @@
       </c>
       <c r="J318" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K318" s="5" t="n">
-        <v>24501350</v>
+        <v>20819800</v>
       </c>
       <c r="L318" s="5" t="n">
-        <v>31493</v>
+        <v>26761</v>
       </c>
       <c r="M318" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N318" s="3" t="inlineStr">
@@ -20918,7 +20910,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2022-01-05</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -20980,7 +20972,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -21042,7 +21034,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
@@ -21104,7 +21096,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -21166,7 +21158,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
@@ -21228,7 +21220,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -21290,7 +21282,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
+          <t>2021-12-19</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -21352,7 +21344,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -21414,7 +21406,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -21476,7 +21468,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -21549,18 +21541,18 @@
       </c>
       <c r="J329" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K329" s="5" t="n">
-        <v>17467465</v>
+        <v>14842820</v>
       </c>
       <c r="L329" s="5" t="n">
-        <v>32347</v>
+        <v>27487</v>
       </c>
       <c r="M329" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N329" s="3" t="inlineStr">
@@ -21611,18 +21603,18 @@
       </c>
       <c r="J330" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K330" s="5" t="n">
-        <v>24427045</v>
+        <v>20756660</v>
       </c>
       <c r="L330" s="5" t="n">
-        <v>31397</v>
+        <v>26680</v>
       </c>
       <c r="M330" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N330" s="3" t="inlineStr">
@@ -21662,7 +21654,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2021-12-28</t>
+          <t>2021-12-29</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -21724,7 +21716,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
+          <t>2021-09-04</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -21786,7 +21778,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2021-11-16</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -21848,7 +21840,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -21972,7 +21964,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -22034,7 +22026,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2022-01-02</t>
+          <t>2022-01-03</t>
         </is>
       </c>
       <c r="H337" s="5" t="n">
@@ -22096,7 +22088,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -22158,7 +22150,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
+          <t>2021-09-04</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -22220,7 +22212,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -22406,7 +22398,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2021-12-29</t>
+          <t>2021-12-30</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -22468,7 +22460,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -22530,7 +22522,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -22592,7 +22584,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -22665,18 +22657,18 @@
       </c>
       <c r="J347" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K347" s="5" t="n">
-        <v>17309205</v>
+        <v>14708340</v>
       </c>
       <c r="L347" s="5" t="n">
-        <v>32054</v>
+        <v>27238</v>
       </c>
       <c r="M347" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N347" s="3" t="inlineStr">
@@ -22778,7 +22770,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2021-12-28</t>
+          <t>2021-12-29</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -22840,7 +22832,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -22902,7 +22894,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
@@ -22964,7 +22956,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -23037,18 +23029,18 @@
       </c>
       <c r="J353" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K353" s="5" t="n">
-        <v>17256130</v>
+        <v>14663240</v>
       </c>
       <c r="L353" s="5" t="n">
-        <v>31956</v>
+        <v>27154</v>
       </c>
       <c r="M353" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N353" s="3" t="inlineStr">
@@ -23088,7 +23080,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -23150,7 +23142,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2021-12-29</t>
+          <t>2021-12-30</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -23212,7 +23204,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -23274,7 +23266,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -23336,7 +23328,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -23522,7 +23514,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2022-01-06</t>
+          <t>2022-01-07</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -23584,7 +23576,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -23646,7 +23638,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H363" s="5" t="n">
@@ -23708,7 +23700,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H364" s="5" t="n">
@@ -23894,7 +23886,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2022-01-05</t>
         </is>
       </c>
       <c r="H367" s="5" t="n">
@@ -23956,7 +23948,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2021-11-25</t>
+          <t>2021-11-26</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
@@ -24018,7 +24010,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2021-12-05</t>
+          <t>2021-12-06</t>
         </is>
       </c>
       <c r="H369" s="5" t="n">
@@ -24080,7 +24072,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H370" s="5" t="n">
@@ -24266,7 +24258,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2022-01-10</t>
+          <t>2022-01-11</t>
         </is>
       </c>
       <c r="H373" s="5" t="n">
@@ -24328,7 +24320,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2022-01-06</t>
+          <t>2022-01-07</t>
         </is>
       </c>
       <c r="H374" s="5" t="n">
@@ -24390,7 +24382,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2022-01-05</t>
         </is>
       </c>
       <c r="H375" s="5" t="n">
@@ -24452,7 +24444,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2021-11-18</t>
+          <t>2021-11-19</t>
         </is>
       </c>
       <c r="H376" s="5" t="n">
@@ -24638,7 +24630,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2022-01-23</t>
+          <t>2022-01-24</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -24700,7 +24692,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2022-03-02</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
@@ -24762,7 +24754,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>2022-01-05</t>
         </is>
       </c>
       <c r="H381" s="5" t="n">
@@ -24824,7 +24816,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2021-11-18</t>
+          <t>2021-11-19</t>
         </is>
       </c>
       <c r="H382" s="5" t="n">
@@ -25010,7 +25002,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2022-01-05</t>
+          <t>2022-01-06</t>
         </is>
       </c>
       <c r="H385" s="5" t="n">
@@ -25072,7 +25064,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2022-02-08</t>
+          <t>2022-02-09</t>
         </is>
       </c>
       <c r="H386" s="5" t="n">
@@ -25134,7 +25126,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2021-11-10</t>
         </is>
       </c>
       <c r="H387" s="5" t="n">
@@ -25196,7 +25188,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2022-01-02</t>
+          <t>2022-01-03</t>
         </is>
       </c>
       <c r="H388" s="5" t="n">
@@ -25382,7 +25374,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2022-02-08</t>
+          <t>2022-02-09</t>
         </is>
       </c>
       <c r="H391" s="5" t="n">
@@ -25444,7 +25436,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2022-07-24</t>
+          <t>2022-07-25</t>
         </is>
       </c>
       <c r="H392" s="5" t="n">
@@ -25506,7 +25498,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2022-01-12</t>
+          <t>2022-01-13</t>
         </is>
       </c>
       <c r="H393" s="5" t="n">
@@ -25568,7 +25560,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H394" s="5" t="n">
@@ -25754,7 +25746,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2022-02-10</t>
+          <t>2022-02-11</t>
         </is>
       </c>
       <c r="H397" s="5" t="n">
@@ -25816,7 +25808,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2022-03-27</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="H398" s="5" t="n">
@@ -25878,7 +25870,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2022-03-27</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="H399" s="5" t="n">
@@ -25940,7 +25932,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2021-09-22</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="H400" s="5" t="n">
@@ -26126,7 +26118,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
+          <t>2022-03-04</t>
         </is>
       </c>
       <c r="H403" s="5" t="n">
@@ -26188,7 +26180,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2022-08-08</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="H404" s="5" t="n">
@@ -26250,7 +26242,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2022-05-02</t>
+          <t>2022-05-03</t>
         </is>
       </c>
       <c r="H405" s="5" t="n">
@@ -26312,7 +26304,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="H406" s="5" t="n">
@@ -26417,7 +26409,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -26427,7 +26419,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>137</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -26521,7 +26513,7 @@
           <t>E | 238呎 (开放式)
 $567万
 $23,804/呎
-(26年-04月-07日)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
@@ -26529,7 +26521,7 @@
           <t>F | 229呎 (开放式)
 $545万
 $23,782/呎
-(26年-04月-29日)</t>
+(26年-04月-30日)</t>
         </is>
       </c>
     </row>
@@ -26560,7 +26552,7 @@
           <t>C | 367呎 (1房)
 $908万
 $24,748/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -26568,7 +26560,7 @@
           <t>D | 356呎 (1房)
 $783万
 $21,995/呎
-(25年-11月-26日)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -26576,7 +26568,7 @@
           <t>E | 238呎 (开放式)
 $563万
 $23,672/呎
-(26年-03月-04日)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -26584,7 +26576,7 @@
           <t>F | 229呎 (开放式)
 $670万
 $29,242/呎
-(22年-08月-25日)</t>
+(22年-08月-26日)</t>
         </is>
       </c>
     </row>
@@ -26615,7 +26607,7 @@
           <t>C | 367呎 (1房)
 $898万
 $24,467/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -26623,7 +26615,7 @@
           <t>D | 356呎 (1房)
 $774万
 $21,747/呎
-(25年-08月-11日)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -26631,7 +26623,7 @@
           <t>E | 238呎 (开放式)
 $524万
 $22,000/呎
-(25年-06月-29日)</t>
+(25年-06月-30日)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -26639,7 +26631,7 @@
           <t>F | 229呎 (开放式)
 $683万
 $29,819/呎
-(21年-10月-10日)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
     </row>
@@ -26670,7 +26662,7 @@
           <t>C | 367呎 (1房)
 $832万
 $22,674/呎
-(25年-08月-10日)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -26678,7 +26670,7 @@
           <t>D | 356呎 (1房)
 $983万
 $27,619/呎
-(21年-10月-10日)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -26686,7 +26678,7 @@
           <t>E | 238呎 (开放式)
 $527万
 $22,125/呎
-(25年-06月-29日)</t>
+(25年-06月-30日)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -26694,7 +26686,7 @@
           <t>F | 229呎 (开放式)
 $515万
 $22,501/呎
-(25年-11月-02日)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
     </row>
@@ -26725,7 +26717,7 @@
           <t>C | 367呎 (1房)
 $830万
 $22,609/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -26733,7 +26725,7 @@
           <t>D | 356呎 (1房)
 $848万
 $23,831/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -26741,7 +26733,7 @@
           <t>E | 238呎 (开放式)
 $683万
 $28,708/呎
-(22年-05月-25日)</t>
+(22年-05月-26日)</t>
         </is>
       </c>
       <c r="G9" s="23" t="inlineStr">
@@ -26759,7 +26751,117 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 775呎 (3房)
+$2600万
+$33,543/呎
+(26年-07月-24日)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$905万
+$24,670/呎
+(26年-02月-10日)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$846万
+$23,763/呎
+(26年-04月-01日)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$518万
+$21,753/呎
+(25年-06月-16日)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$512万
+$22,368/呎
+(25年-11月-21日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 775呎 (3房)
+$2592万
+$33,443/呎
+(26年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$903万
+$24,601/呎
+(26年-02月-24日)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$844万
+$23,695/呎
+(26年-04月-01日)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$522万
+$21,939/呎
+(25年-06月-16日)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$511万
+$22,303/呎
+(25年-10月-20日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 776呎 (3房)
 招标单位
@@ -26767,7 +26869,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>B | 541呎 (2房)
 -
@@ -26775,54 +26877,54 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>C | 367呎 (1房)
-$905万
-$24,670/呎
-(26年-02月-09日)</t>
-        </is>
-      </c>
-      <c r="E10" s="22" t="inlineStr">
+$883万
+$24,048/呎
+(26年-02月-06日)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>D | 356呎 (1房)
-$846万
-$23,763/呎
-(26年-03月-31日)</t>
-        </is>
-      </c>
-      <c r="F10" s="22" t="inlineStr">
+$825万
+$23,162/呎
+(26年-02月-13日)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>E | 238呎 (开放式)
-$518万
-$21,753/呎
-(25年-06月-15日)</t>
-        </is>
-      </c>
-      <c r="G10" s="22" t="inlineStr">
+$678万
+$28,468/呎
+(22年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t>F | 229呎 (开放式)
-$512万
-$22,368/呎
-(25年-11月-20日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B11" s="22" t="inlineStr">
-        <is>
-          <t>A | 775呎 (3房)
-$2592万
-$33,443/呎
-(26年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="inlineStr">
+$650万
+$28,404/呎
+(22年-05月-26日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 541呎 (2房)
 -
@@ -26830,46 +26932,156 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 367呎 (1房)
-$903万
-$24,601/呎
-(26年-02月-23日)</t>
-        </is>
-      </c>
-      <c r="E11" s="22" t="inlineStr">
+$880万
+$23,977/呎
+(26年-02月-13日)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>D | 356呎 (1房)
-$844万
-$23,695/呎
-(26年-03月-31日)</t>
-        </is>
-      </c>
-      <c r="F11" s="22" t="inlineStr">
+$822万
+$23,094/呎
+(26年-02月-13日)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>E | 238呎 (开放式)
-$522万
-$21,939/呎
-(25年-06月-15日)</t>
-        </is>
-      </c>
-      <c r="G11" s="22" t="inlineStr">
+$513万
+$21,570/呎
+(25年-06月-17日)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>F | 229呎 (开放式)
-$511万
-$22,303/呎
-(25年-10月-19日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
+$508万
+$22,173/呎
+(25年-06月-20日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$818万
+$22,283/呎
+(25年-08月-06日)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$820万
+$23,029/呎
+(26年-02月-13日)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$674万
+$28,320/呎
+(22年-04月-25日)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$667万
+$29,126/呎
+(21年-11月-15日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 775呎 (3房)
+$2522万
+$32,542/呎
+(26年-05月-12日)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$815万
+$22,216/呎
+(25年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$834万
+$23,418/呎
+(26年-03月-26日)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$686万
+$28,827/呎
+(21年-09月-28日)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$645万
+$28,152/呎
+(22年-01月-31日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 776呎 (3房)
 招标单位
@@ -26877,7 +27089,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>B | 541呎 (2房)
 -
@@ -26885,46 +27097,46 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 367呎 (1房)
-$883万
-$24,048/呎
-(26年-02月-05日)</t>
-        </is>
-      </c>
-      <c r="E12" s="22" t="inlineStr">
+$813万
+$22,151/呎
+(25年-07月-04日)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>D | 356呎 (1房)
-$825万
-$23,162/呎
-(26年-02月-12日)</t>
-        </is>
-      </c>
-      <c r="F12" s="22" t="inlineStr">
+$831万
+$23,350/呎
+(26年-03月-24日)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>E | 238呎 (开放式)
-$678万
-$28,468/呎
-(22年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="G12" s="22" t="inlineStr">
+$684万
+$28,745/呎
+(21年-09月-28日)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>F | 229呎 (开放式)
 $650万
-$28,404/呎
-(22年-05月-25日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
+$28,364/呎
+(22年-01月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>A | 776呎 (3房)
 -
@@ -26932,7 +27144,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>B | 541呎 (2房)
 -
@@ -26940,46 +27152,46 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 367呎 (1房)
-$880万
-$23,977/呎
-(26年-02月-12日)</t>
-        </is>
-      </c>
-      <c r="E13" s="22" t="inlineStr">
+$808万
+$22,020/呎
+(25年-06月-27日)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>D | 356呎 (1房)
-$822万
-$23,094/呎
-(26年-02月-12日)</t>
-        </is>
-      </c>
-      <c r="F13" s="22" t="inlineStr">
+$826万
+$23,212/呎
+(26年-03月-27日)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>E | 238呎 (开放式)
-$513万
-$21,570/呎
-(25年-06月-16日)</t>
-        </is>
-      </c>
-      <c r="G13" s="22" t="inlineStr">
+$659万
+$27,705/呎
+(22年-01月-26日)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>F | 229呎 (开放式)
-$508万
-$22,173/呎
-(25年-06月-19日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
+$659万
+$28,783/呎
+(21年-11月-02日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>A | 776呎 (3房)
 -
@@ -26987,7 +27199,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>B | 541呎 (2房)
 -
@@ -26995,54 +27207,54 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 367呎 (1房)
-$818万
-$22,283/呎
-(25年-08月-05日)</t>
-        </is>
-      </c>
-      <c r="E14" s="22" t="inlineStr">
+$838万
+$22,832/呎
+(25年-06月-27日)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>D | 356呎 (1房)
-$820万
-$23,029/呎
-(26年-02月-12日)</t>
-        </is>
-      </c>
-      <c r="F14" s="22" t="inlineStr">
+$824万
+$23,144/呎
+(26年-02月-23日)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>E | 238呎 (开放式)
-$674万
-$28,320/呎
-(22年-04月-24日)</t>
-        </is>
-      </c>
-      <c r="G14" s="22" t="inlineStr">
+$664万
+$27,916/呎
+(21年-09月-28日)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
         <is>
           <t>F | 229呎 (开放式)
-$667万
-$29,126/呎
-(21年-11月-14日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B15" s="22" t="inlineStr">
-        <is>
-          <t>A | 775呎 (3房)
-$2522万
-$32,542/呎
-(26年-05月-11日)</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="inlineStr">
+$657万
+$28,694/呎
+(21年-11月-02日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>B | 541呎 (2房)
 -
@@ -27050,46 +27262,211 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>C | 367呎 (1房)
-$815万
-$22,216/呎
-(25年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="E15" s="22" t="inlineStr">
+$803万
+$21,889/呎
+(25年-07月-04日)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>D | 356呎 (1房)
-$834万
-$23,418/呎
-(26年-03月-25日)</t>
-        </is>
-      </c>
-      <c r="F15" s="22" t="inlineStr">
+$979万
+$27,509/呎
+(21年-10月-11日)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>E | 238呎 (开放式)
-$686万
-$28,827/呎
+$676万
+$28,416/呎
+(21年-09月-28日)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$642万
+$28,024/呎
+(21年-11月-09日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 775呎 (3房)
+$2483万
+$32,041/呎
+(26年-03月-26日)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$1077万
+$29,343/呎
+(22年-10月-26日)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$956万
+$26,866/呎
+(22年-02月-16日)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$674万
+$28,333/呎
+(21年-09月-28日)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$653万
+$28,523/呎
+(21年-10月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$1041万
+$28,378/呎
+(23年-02月-03日)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$944万
+$26,506/呎
+(22年-02月-15日)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$672万
+$28,251/呎
+(21年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$631万
+$27,566/呎
+(21年-10月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$1060万
+$28,877/呎
+(23年-05月-10日)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$951万
+$26,704/呎
+(22年-01月-03日)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$650万
+$27,306/呎
 (21年-09月-27日)</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="G22" s="22" t="inlineStr">
         <is>
           <t>F | 229呎 (开放式)
-$645万
-$28,152/呎
-(22年-01月-30日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
+$649万
+$28,352/呎
+(21年-10月-11日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 776呎 (3房)
 招标单位
@@ -27097,7 +27474,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>B | 541呎 (2房)
 -
@@ -27105,46 +27482,101 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>C | 367呎 (1房)
-$813万
-$22,151/呎
-(25年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="E16" s="22" t="inlineStr">
+$794万
+$21,627/呎
+(25年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>D | 356呎 (1房)
-$831万
-$23,350/呎
-(26年-03月-23日)</t>
-        </is>
-      </c>
-      <c r="F16" s="22" t="inlineStr">
+$958万
+$26,904/呎
+(22年-01月-21日)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>E | 238呎 (开放式)
-$684万
-$28,745/呎
-(21年-09月-27日)</t>
-        </is>
-      </c>
-      <c r="G16" s="22" t="inlineStr">
+$668万
+$28,086/呎
+(21年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
         <is>
           <t>F | 229呎 (开放式)
-$650万
-$28,364/呎
-(22年-01月-11日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B17" s="21" t="inlineStr">
+$654万
+$28,550/呎
+(21年-09月-20日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$1011万
+$27,542/呎
+(23年-01月-17日)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$965万
+$27,099/呎
+(21年-10月-12日)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$646万
+$27,147/呎
+(21年-09月-28日)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$645万
+$28,176/呎
+(21年-10月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 776呎 (3房)
 -
@@ -27152,7 +27584,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 541呎 (2房)
 -
@@ -27160,46 +27592,46 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>C | 367呎 (1房)
-$808万
-$22,020/呎
-(25年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="E17" s="22" t="inlineStr">
+$1021万
+$27,832/呎
+(21年-10月-12日)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>D | 356呎 (1房)
-$826万
-$23,212/呎
-(26年-03月-26日)</t>
-        </is>
-      </c>
-      <c r="F17" s="22" t="inlineStr">
+$965万
+$27,099/呎
+(21年-10月-12日)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>E | 238呎 (开放式)
-$659万
-$27,705/呎
-(22年-01月-25日)</t>
-        </is>
-      </c>
-      <c r="G17" s="22" t="inlineStr">
+$660万
+$27,718/呎
+(21年-09月-27日)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
         <is>
           <t>F | 229呎 (开放式)
-$659万
-$28,783/呎
-(21年-11月-01日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B18" s="21" t="inlineStr">
+$645万
+$28,176/呎
+(21年-10月-19日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>A | 776呎 (3房)
 -
@@ -27207,7 +27639,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>B | 541呎 (2房)
 -
@@ -27215,46 +27647,101 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>C | 367呎 (1房)
-$838万
-$22,832/呎
-(25年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="E18" s="22" t="inlineStr">
+$1040万
+$28,326/呎
+(23年-03月-10日)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>D | 356呎 (1房)
-$824万
-$23,144/呎
-(26年-02月-22日)</t>
-        </is>
-      </c>
-      <c r="F18" s="22" t="inlineStr">
+$962万
+$27,016/呎
+(21年-10月-25日)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>E | 238呎 (开放式)
-$664万
-$27,916/呎
-(21年-09月-27日)</t>
-        </is>
-      </c>
-      <c r="G18" s="22" t="inlineStr">
+$644万
+$27,067/呎
+(21年-09月-28日)</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
         <is>
           <t>F | 229呎 (开放式)
-$657万
-$28,694/呎
-(21年-11月-01日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr">
+$624万
+$27,231/呎
+(21年-10月-11日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$1047万
+$28,529/呎
+(22年-10月-18日)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$949万
+$26,658/呎
+(22年-01月-05日)</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$663万
+$27,839/呎
+(21年-09月-28日)</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$641万
+$28,005/呎
+(21年-10月-15日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 776呎 (3房)
 招标单位
@@ -27262,7 +27749,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 541呎 (2房)
 -
@@ -27270,54 +27757,54 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D19" s="22" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>C | 367呎 (1房)
-$803万
-$21,889/呎
-(25年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="E19" s="22" t="inlineStr">
+$1012万
+$27,581/呎
+(22年-02月-11日)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>D | 356呎 (1房)
-$979万
-$27,509/呎
-(21年-10月-10日)</t>
-        </is>
-      </c>
-      <c r="F19" s="22" t="inlineStr">
+$956万
+$26,851/呎
+(22年-01月-27日)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
         <is>
           <t>E | 238呎 (开放式)
-$676万
-$28,416/呎
+$661万
+$27,757/呎
 (21年-09月-27日)</t>
         </is>
       </c>
-      <c r="G19" s="22" t="inlineStr">
+      <c r="G28" s="22" t="inlineStr">
         <is>
           <t>F | 229呎 (开放式)
-$642万
-$28,024/呎
-(21年-11月-08日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B20" s="22" t="inlineStr">
-        <is>
-          <t>A | 775呎 (3房)
-$2483万
-$32,041/呎
-(26年-03月-25日)</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="inlineStr">
+$639万
+$27,919/呎
+(21年-10月-20日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
         <is>
           <t>B | 541呎 (2房)
 -
@@ -27325,46 +27812,46 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D20" s="22" t="inlineStr">
+      <c r="D29" s="22" t="inlineStr">
         <is>
           <t>C | 367呎 (1房)
-$1077万
-$29,343/呎
-(22年-10月-25日)</t>
-        </is>
-      </c>
-      <c r="E20" s="22" t="inlineStr">
+$999万
+$27,208/呎
+(22年-04月-14日)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
         <is>
           <t>D | 356呎 (1房)
-$956万
-$26,866/呎
-(22年-02月-15日)</t>
-        </is>
-      </c>
-      <c r="F20" s="22" t="inlineStr">
+$943万
+$26,498/呎
+(21年-10月-05日)</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
         <is>
           <t>E | 238呎 (开放式)
-$674万
-$28,333/呎
-(21年-09月-27日)</t>
-        </is>
-      </c>
-      <c r="G20" s="22" t="inlineStr">
+$665万
+$27,957/呎
+(21年-09月-04日)</t>
+        </is>
+      </c>
+      <c r="G29" s="22" t="inlineStr">
         <is>
           <t>F | 229呎 (开放式)
-$653万
-$28,523/呎
+$644万
+$28,113/呎
 (21年-10月-11日)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B21" s="21" t="inlineStr">
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
         <is>
           <t>A | 776呎 (3房)
 -
@@ -27372,7 +27859,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="C30" s="21" t="inlineStr">
         <is>
           <t>B | 541呎 (2房)
 -
@@ -27380,46 +27867,156 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D30" s="22" t="inlineStr">
         <is>
           <t>C | 367呎 (1房)
-$1041万
-$28,378/呎
-(23年-02月-02日)</t>
-        </is>
-      </c>
-      <c r="E21" s="22" t="inlineStr">
+$1004万
+$27,356/呎
+(21年-10月-06日)</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
         <is>
           <t>D | 356呎 (1房)
-$944万
-$26,506/呎
-(22年-02月-14日)</t>
-        </is>
-      </c>
-      <c r="F21" s="22" t="inlineStr">
+$918万
+$25,791/呎
+(21年-10月-04日)</t>
+        </is>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
         <is>
           <t>E | 238呎 (开放式)
-$672万
-$28,251/呎
-(21年-09月-28日)</t>
-        </is>
-      </c>
-      <c r="G21" s="22" t="inlineStr">
+$641万
+$26,948/呎
+(21年-09月-04日)</t>
+        </is>
+      </c>
+      <c r="G30" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$635万
+$27,748/呎
+(21年-11月-01日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$980万
+$26,709/呎
+(21年-10月-05日)</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$915万
+$25,711/呎
+(21年-10月-08日)</t>
+        </is>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$633万
+$26,588/呎
+(21年-09月-24日)</t>
+        </is>
+      </c>
+      <c r="G31" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$612万
+$26,728/呎
+(22年-01月-05日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$991万
+$26,990/呎
+(21年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$915万
+$25,711/呎
+(22年-01月-17日)</t>
+        </is>
+      </c>
+      <c r="F32" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$639万
+$26,868/呎
+(22年-05月-23日)</t>
+        </is>
+      </c>
+      <c r="G32" s="22" t="inlineStr">
         <is>
           <t>F | 229呎 (开放式)
 $631万
-$27,566/呎
-(21年-10月-11日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="inlineStr">
+$27,572/呎
+(21年-12月-14日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="inlineStr">
         <is>
           <t>A | 776呎 (3房)
 -
@@ -27427,7 +28024,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="C33" s="21" t="inlineStr">
         <is>
           <t>B | 541呎 (2房)
 -
@@ -27435,54 +28032,54 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D33" s="22" t="inlineStr">
         <is>
           <t>C | 367呎 (1房)
-$1060万
-$28,877/呎
-(23年-05月-09日)</t>
-        </is>
-      </c>
-      <c r="E22" s="22" t="inlineStr">
+$998万
+$27,186/呎
+(21年-10月-06日)</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
         <is>
           <t>D | 356呎 (1房)
-$951万
-$26,704/呎
-(22年-01月-02日)</t>
-        </is>
-      </c>
-      <c r="F22" s="22" t="inlineStr">
+$922万
+$25,901/呎
+(22年-01月-24日)</t>
+        </is>
+      </c>
+      <c r="F33" s="22" t="inlineStr">
         <is>
           <t>E | 238呎 (开放式)
-$650万
-$27,306/呎
-(21年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="G22" s="22" t="inlineStr">
+$631万
+$26,508/呎
+(22年-05月-23日)</t>
+        </is>
+      </c>
+      <c r="G33" s="22" t="inlineStr">
         <is>
           <t>F | 229呎 (开放式)
-$649万
-$28,352/呎
-(21年-10月-10日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
+$629万
+$27,487/呎
+(22年-01月-14日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B34" s="21" t="inlineStr">
         <is>
           <t>A | 776呎 (3房)
-招标单位
 -
-(在售)</t>
-        </is>
-      </c>
-      <c r="C23" s="21" t="inlineStr">
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C34" s="21" t="inlineStr">
         <is>
           <t>B | 541呎 (2房)
 -
@@ -27490,54 +28087,54 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D34" s="22" t="inlineStr">
         <is>
           <t>C | 367呎 (1房)
-$794万
-$21,627/呎
-(25年-07月-01日)</t>
-        </is>
-      </c>
-      <c r="E23" s="22" t="inlineStr">
+$984万
+$26,822/呎
+(21年-10月-07日)</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
         <is>
           <t>D | 356呎 (1房)
-$958万
-$26,904/呎
-(22年-01月-20日)</t>
-        </is>
-      </c>
-      <c r="F23" s="22" t="inlineStr">
+$767万
+$21,545/呎
+(26年-02月-09日)</t>
+        </is>
+      </c>
+      <c r="F34" s="22" t="inlineStr">
         <is>
           <t>E | 238呎 (开放式)
-$668万
-$28,086/呎
-(21年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="G23" s="22" t="inlineStr">
+$625万
+$26,268/呎
+(23年-03月-10日)</t>
+        </is>
+      </c>
+      <c r="G34" s="22" t="inlineStr">
         <is>
           <t>F | 229呎 (开放式)
-$654万
-$28,550/呎
-(21年-09月-19日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
+$611万
+$26,670/呎
+(22年-04月-01日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B35" s="21" t="inlineStr">
         <is>
           <t>A | 776呎 (3房)
-招标单位
 -
-(在售)</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C35" s="21" t="inlineStr">
         <is>
           <t>B | 541呎 (2房)
 -
@@ -27545,46 +28142,46 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="D35" s="22" t="inlineStr">
         <is>
           <t>C | 367呎 (1房)
-$1011万
-$27,542/呎
-(23年-01月-16日)</t>
-        </is>
-      </c>
-      <c r="E24" s="22" t="inlineStr">
+$991万
+$27,014/呎
+(21年-10月-08日)</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
         <is>
           <t>D | 356呎 (1房)
-$965万
-$27,099/呎
-(21年-10月-11日)</t>
-        </is>
-      </c>
-      <c r="F24" s="22" t="inlineStr">
+$760万
+$21,342/呎
+(26年-02月-09日)</t>
+        </is>
+      </c>
+      <c r="F35" s="22" t="inlineStr">
         <is>
           <t>E | 238呎 (开放式)
-$646万
-$27,147/呎
-(21年-09月-27日)</t>
-        </is>
-      </c>
-      <c r="G24" s="22" t="inlineStr">
+$633万
+$26,577/呎
+(23年-06月-14日)</t>
+        </is>
+      </c>
+      <c r="G35" s="22" t="inlineStr">
         <is>
           <t>F | 229呎 (开放式)
-$645万
-$28,176/呎
-(21年-10月-11日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B25" s="21" t="inlineStr">
+$599万
+$26,139/呎
+(21年-11月-16日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B36" s="21" t="inlineStr">
         <is>
           <t>A | 776呎 (3房)
 -
@@ -27592,7 +28189,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C36" s="21" t="inlineStr">
         <is>
           <t>B | 541呎 (2房)
 -
@@ -27600,46 +28197,46 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D36" s="22" t="inlineStr">
         <is>
           <t>C | 367呎 (1房)
-$1021万
-$27,832/呎
-(21年-10月-11日)</t>
-        </is>
-      </c>
-      <c r="E25" s="22" t="inlineStr">
+$965万
+$26,292/呎
+(21年-10月-12日)</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
         <is>
           <t>D | 356呎 (1房)
-$965万
-$27,099/呎
-(21年-10月-11日)</t>
-        </is>
-      </c>
-      <c r="F25" s="22" t="inlineStr">
+$757万
+$21,276/呎
+(26年-02月-09日)</t>
+        </is>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
         <is>
           <t>E | 238呎 (开放式)
-$660万
-$27,718/呎
-(21年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="G25" s="22" t="inlineStr">
+$569万
+$23,900/呎
+(24年-07月-19日)</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="inlineStr">
         <is>
           <t>F | 229呎 (开放式)
-$645万
-$28,176/呎
-(21年-10月-18日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B26" s="21" t="inlineStr">
+$597万
+$26,056/呎
+(21年-12月-15日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B37" s="21" t="inlineStr">
         <is>
           <t>A | 776呎 (3房)
 -
@@ -27647,7 +28244,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="C37" s="21" t="inlineStr">
         <is>
           <t>B | 541呎 (2房)
 -
@@ -27655,617 +28252,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$1040万
-$28,326/呎
-(23年-03月-09日)</t>
-        </is>
-      </c>
-      <c r="E26" s="22" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$962万
-$27,016/呎
-(21年-10月-24日)</t>
-        </is>
-      </c>
-      <c r="F26" s="22" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$644万
-$27,067/呎
-(21年-09月-27日)</t>
-        </is>
-      </c>
-      <c r="G26" s="22" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$624万
-$27,231/呎
-(21年-10月-10日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="58" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B27" s="21" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C27" s="21" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D27" s="22" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$1047万
-$28,529/呎
-(22年-10月-17日)</t>
-        </is>
-      </c>
-      <c r="E27" s="22" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$949万
-$26,658/呎
-(22年-01月-04日)</t>
-        </is>
-      </c>
-      <c r="F27" s="22" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$663万
-$27,839/呎
-(21年-09月-27日)</t>
-        </is>
-      </c>
-      <c r="G27" s="22" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$641万
-$28,005/呎
-(21年-10月-14日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C28" s="21" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D28" s="22" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$1012万
-$27,581/呎
-(22年-02月-10日)</t>
-        </is>
-      </c>
-      <c r="E28" s="22" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$956万
-$26,851/呎
-(22年-01月-26日)</t>
-        </is>
-      </c>
-      <c r="F28" s="22" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$661万
-$27,757/呎
-(21年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="G28" s="22" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$639万
-$27,919/呎
-(21年-10月-19日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B29" s="20" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C29" s="21" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D29" s="22" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$999万
-$27,208/呎
-(22年-04月-13日)</t>
-        </is>
-      </c>
-      <c r="E29" s="22" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$943万
-$26,498/呎
-(21年-10月-04日)</t>
-        </is>
-      </c>
-      <c r="F29" s="22" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$665万
-$27,957/呎
-(21年-09月-03日)</t>
-        </is>
-      </c>
-      <c r="G29" s="22" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$644万
-$28,113/呎
-(21年-10月-10日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="58" customHeight="1">
-      <c r="A30" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B30" s="21" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C30" s="21" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D30" s="22" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$1004万
-$27,356/呎
-(21年-10月-05日)</t>
-        </is>
-      </c>
-      <c r="E30" s="22" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$918万
-$25,791/呎
-(21年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="F30" s="22" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$641万
-$26,948/呎
-(21年-09月-03日)</t>
-        </is>
-      </c>
-      <c r="G30" s="22" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$635万
-$27,748/呎
-(21年-10月-31日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C31" s="21" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D31" s="22" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$980万
-$26,709/呎
-(21年-10月-04日)</t>
-        </is>
-      </c>
-      <c r="E31" s="22" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$915万
-$25,711/呎
-(21年-10月-07日)</t>
-        </is>
-      </c>
-      <c r="F31" s="22" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$633万
-$26,588/呎
-(21年-09月-23日)</t>
-        </is>
-      </c>
-      <c r="G31" s="22" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$612万
-$26,728/呎
-(22年-01月-04日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="58" customHeight="1">
-      <c r="A32" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B32" s="20" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C32" s="21" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D32" s="22" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$991万
-$26,990/呎
-(21年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="E32" s="22" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$915万
-$25,711/呎
-(22年-01月-16日)</t>
-        </is>
-      </c>
-      <c r="F32" s="22" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$639万
-$26,868/呎
-(22年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="G32" s="22" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$631万
-$27,572/呎
-(21年-12月-13日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="58" customHeight="1">
-      <c r="A33" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B33" s="21" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C33" s="21" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D33" s="22" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$998万
-$27,186/呎
-(21年-10月-05日)</t>
-        </is>
-      </c>
-      <c r="E33" s="22" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$922万
-$25,901/呎
-(22年-01月-23日)</t>
-        </is>
-      </c>
-      <c r="F33" s="22" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$631万
-$26,508/呎
-(22年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="G33" s="22" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$629万
-$27,487/呎
-(22年-01月-13日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="58" customHeight="1">
-      <c r="A34" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B34" s="21" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C34" s="21" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D34" s="22" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$984万
-$26,822/呎
-(21年-10月-06日)</t>
-        </is>
-      </c>
-      <c r="E34" s="22" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$767万
-$21,545/呎
-(26年-02月-08日)</t>
-        </is>
-      </c>
-      <c r="F34" s="22" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$625万
-$26,268/呎
-(23年-03月-09日)</t>
-        </is>
-      </c>
-      <c r="G34" s="22" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$611万
-$26,670/呎
-(22年-03月-31日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="58" customHeight="1">
-      <c r="A35" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B35" s="21" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C35" s="21" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D35" s="22" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$991万
-$27,014/呎
-(21年-10月-07日)</t>
-        </is>
-      </c>
-      <c r="E35" s="22" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$760万
-$21,342/呎
-(26年-02月-08日)</t>
-        </is>
-      </c>
-      <c r="F35" s="22" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$633万
-$26,577/呎
-(23年-06月-13日)</t>
-        </is>
-      </c>
-      <c r="G35" s="22" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$599万
-$26,139/呎
-(21年-11月-15日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="58" customHeight="1">
-      <c r="A36" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B36" s="21" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C36" s="21" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D36" s="22" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$965万
-$26,292/呎
-(21年-10月-11日)</t>
-        </is>
-      </c>
-      <c r="E36" s="22" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$757万
-$21,276/呎
-(26年-02月-08日)</t>
-        </is>
-      </c>
-      <c r="F36" s="22" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$569万
-$23,900/呎
-(24年-07月-18日)</t>
-        </is>
-      </c>
-      <c r="G36" s="22" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$597万
-$26,056/呎
-(21年-12月-14日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="58" customHeight="1">
-      <c r="A37" s="19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B37" s="21" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C37" s="21" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="D37" s="22" t="inlineStr">
         <is>
           <t>C | 367呎 (1房)
 $969万
 $26,401/呎
-(22年-01月-04日)</t>
+(22年-01月-05日)</t>
         </is>
       </c>
       <c r="E37" s="22" t="inlineStr">
@@ -28273,7 +28265,7 @@
           <t>D | 356呎 (1房)
 $753万
 $21,140/呎
-(26年-02月-08日)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="F37" s="22" t="inlineStr">
@@ -28281,7 +28273,7 @@
           <t>E | 238呎 (开放式)
 $466万
 $19,595/呎
-(25年-06月-22日)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="G37" s="22" t="inlineStr">
@@ -28289,7 +28281,7 @@
           <t>F | 229呎 (开放式)
 $599万
 $26,163/呎
-(22年-02月-09日)</t>
+(22年-02月-10日)</t>
         </is>
       </c>
     </row>
@@ -28306,7 +28298,7 @@
           <t>C | 374呎 (1房)
 $971万
 $25,957/呎
-(22年-08月-28日)</t>
+(22年-08月-29日)</t>
         </is>
       </c>
       <c r="E38" s="22" t="inlineStr">
@@ -28314,7 +28306,7 @@
           <t>D | 356呎 (1房)
 $745万
 $20,937/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
@@ -28322,7 +28314,7 @@
           <t>E | 238呎 (开放式)
 $462万
 $19,415/呎
-(25年-06月-22日)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="G38" s="22" t="inlineStr">
@@ -28330,7 +28322,7 @@
           <t>F | 229呎 (开放式)
 $587万
 $25,654/呎
-(22年-03月-06日)</t>
+(22年-03月-07日)</t>
         </is>
       </c>
     </row>
@@ -28512,7 +28504,7 @@
           <t>E | 238呎 (开放式)
 $561万
 $23,563/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="G5" s="23" t="inlineStr">
@@ -28535,7 +28527,7 @@
           <t>A | 777呎 (3房)
 $2572万
 $33,107/呎
-(26年-02月-10日)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -28551,7 +28543,7 @@
           <t>C | 367呎 (1房)
 $1073万
 $29,227/呎
-(21年-09月-26日)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -28559,7 +28551,7 @@
           <t>D | 356呎 (1房)
 $776万
 $21,801/呎
-(25年-10月-16日)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -28567,7 +28559,7 @@
           <t>E | 238呎 (开放式)
 $558万
 $23,435/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -28575,7 +28567,7 @@
           <t>F | 229呎 (开放式)
 $644万
 $28,131/呎
-(22年-01月-13日)</t>
+(22年-01月-14日)</t>
         </is>
       </c>
     </row>
@@ -28590,7 +28582,7 @@
           <t>A | 778呎 (3房)
 $2543万
 $32,689/呎
-(22年-03月-06日)</t>
+(22年-03月-07日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -28606,7 +28598,7 @@
           <t>C | 367呎 (1房)
 $1039万
 $28,306/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -28614,7 +28606,7 @@
           <t>D | 356呎 (1房)
 $990万
 $27,818/呎
-(21年-09月-26日)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -28622,7 +28614,7 @@
           <t>E | 238呎 (开放式)
 $518万
 $21,772/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -28630,7 +28622,7 @@
           <t>F | 229呎 (开放式)
 $499万
 $21,772/呎
-(25年-07月-27日)</t>
+(25年-07月-28日)</t>
         </is>
       </c>
     </row>
@@ -28645,7 +28637,7 @@
           <t>A | 777呎 (3房)
 $2582万
 $33,230/呎
-(23年-01月-25日)</t>
+(23年-01月-26日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -28661,7 +28653,7 @@
           <t>C | 367呎 (1房)
 $1055万
 $28,738/呎
-(21年-12月-09日)</t>
+(21年-12月-10日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -28669,7 +28661,7 @@
           <t>D | 356呎 (1房)
 $763万
 $21,428/呎
-(25年-07月-31日)</t>
+(25年-08月-01日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -28677,7 +28669,7 @@
           <t>E | 238呎 (开放式)
 $515万
 $21,650/呎
-(25年-06月-23日)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -28685,7 +28677,7 @@
           <t>F | 229呎 (开放式)
 $496万
 $21,642/呎
-(25年-07月-17日)</t>
+(25年-07月-18日)</t>
         </is>
       </c>
     </row>
@@ -28700,7 +28692,7 @@
           <t>A | 777呎 (3房)
 $2521万
 $32,450/呎
-(22年-06月-12日)</t>
+(22年-06月-13日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -28708,7 +28700,7 @@
           <t>B | 540呎 (2房)
 $1803万
 $33,385/呎
-(24年-04月-15日)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -28716,7 +28708,7 @@
           <t>C | 367呎 (1房)
 $1030万
 $28,065/呎
-(21年-12月-07日)</t>
+(21年-12月-08日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -28724,7 +28716,7 @@
           <t>D | 356呎 (1房)
 $761万
 $21,366/呎
-(25年-07月-31日)</t>
+(25年-08月-01日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -28732,7 +28724,7 @@
           <t>E | 238呎 (开放式)
 $514万
 $21,588/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -28740,7 +28732,7 @@
           <t>F | 229呎 (开放式)
 $581万
 $25,386/呎
-(24年-08月-18日)</t>
+(24年-08月-19日)</t>
         </is>
       </c>
     </row>
@@ -28755,7 +28747,7 @@
           <t>A | 778呎 (3房)
 $2541万
 $32,655/呎
-(21年-10月-11日)</t>
+(21年-10月-12日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -28771,7 +28763,7 @@
           <t>C | 367呎 (1房)
 $1027万
 $27,985/呎
-(22年-01月-03日)</t>
+(22年-01月-04日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -28779,7 +28771,7 @@
           <t>D | 356呎 (1房)
 $979万
 $27,497/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -28787,7 +28779,7 @@
           <t>E | 238呎 (开放式)
 $512万
 $21,529/呎
-(25年-06月-29日)</t>
+(25年-06月-30日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -28795,7 +28787,7 @@
           <t>F | 229呎 (开放式)
 $580万
 $25,314/呎
-(24年-04月-22日)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -28810,7 +28802,7 @@
           <t>A | 777呎 (3房)
 $2507万
 $32,263/呎
-(24年-10月-01日)</t>
+(24年-10月-02日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -28826,7 +28818,7 @@
           <t>C | 367呎 (1房)
 $1024万
 $27,905/呎
-(21年-12月-19日)</t>
+(21年-12月-20日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -28834,7 +28826,7 @@
           <t>D | 356呎 (1房)
 $756万
 $21,241/呎
-(25年-07月-31日)</t>
+(25年-08月-01日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -28842,7 +28834,7 @@
           <t>E | 238呎 (开放式)
 $511万
 $21,467/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -28850,7 +28842,7 @@
           <t>F | 229呎 (开放式)
 $654万
 $28,554/呎
-(22年-08月-10日)</t>
+(22年-08月-11日)</t>
         </is>
       </c>
     </row>
@@ -28865,7 +28857,7 @@
           <t>A | 778呎 (3房)
 $2526万
 $32,466/呎
-(21年-09月-26日)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -28873,7 +28865,7 @@
           <t>B | 540呎 (2房)
 $1806万
 $33,445/呎
-(22年-02月-10日)</t>
+(22年-02月-11日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -28881,7 +28873,7 @@
           <t>C | 367呎 (1房)
 $1021万
 $27,827/呎
-(21年-12月-19日)</t>
+(21年-12月-20日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -28889,7 +28881,7 @@
           <t>D | 356呎 (1房)
 $754万
 $21,177/呎
-(25年-07月-03日)</t>
+(25年-07月-04日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -28897,7 +28889,7 @@
           <t>E | 238呎 (开放式)
 $509万
 $21,404/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -28905,7 +28897,7 @@
           <t>F | 229呎 (开放式)
 $626万
 $27,322/呎
-(22年-06月-05日)</t>
+(22年-06月-06日)</t>
         </is>
       </c>
     </row>
@@ -28920,7 +28912,7 @@
           <t>A | 777呎 (3房)
 $2532万
 $32,581/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -28928,7 +28920,7 @@
           <t>B | 540呎 (2房)
 $1782万
 $33,000/呎
-(21年-10月-17日)</t>
+(21年-10月-18日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -28936,7 +28928,7 @@
           <t>C | 367呎 (1房)
 $1029万
 $28,039/呎
-(21年-09月-26日)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -28944,7 +28936,7 @@
           <t>D | 356呎 (1房)
 $752万
 $21,115/呎
-(25年-06月-22日)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -28952,7 +28944,7 @@
           <t>E | 238呎 (开放式)
 $508万
 $21,364/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -28960,7 +28952,7 @@
           <t>F | 229呎 (开放式)
 $630万
 $27,525/呎
-(22年-05月-25日)</t>
+(22年-05月-26日)</t>
         </is>
       </c>
     </row>
@@ -28975,7 +28967,7 @@
           <t>A | 777呎 (3房)
 $2485万
 $31,981/呎
-(24年-12月-02日)</t>
+(24年-12月-03日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -28983,7 +28975,7 @@
           <t>B | 540呎 (2房)
 $1814万
 $33,596/呎
-(21年-10月-10日)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -28991,7 +28983,7 @@
           <t>C | 367呎 (1房)
 $1015万
 $27,666/呎
-(21年-09月-26日)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -28999,7 +28991,7 @@
           <t>D | 356呎 (1房)
 $750万
 $21,054/呎
-(25年-07月-22日)</t>
+(25年-07月-23日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -29007,7 +28999,7 @@
           <t>E | 238呎 (开放式)
 $660万
 $27,729/呎
-(22年-05月-17日)</t>
+(22年-05月-18日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -29015,7 +29007,7 @@
           <t>F | 229呎 (开放式)
 $629万
 $27,446/呎
-(22年-05月-25日)</t>
+(22年-05月-26日)</t>
         </is>
       </c>
     </row>
@@ -29030,7 +29022,7 @@
           <t>A | 777呎 (3房)
 $2478万
 $31,888/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -29038,7 +29030,7 @@
           <t>B | 540呎 (2房)
 $1791万
 $33,163/呎
-(21年-09月-26日)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -29046,7 +29038,7 @@
           <t>C | 367呎 (1房)
 $1055万
 $28,748/呎
-(21年-12月-02日)</t>
+(21年-12月-03日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -29054,7 +29046,7 @@
           <t>D | 356呎 (1房)
 $747万
 $20,992/呎
-(25年-06月-24日)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -29062,7 +29054,7 @@
           <t>E | 238呎 (开放式)
 $509万
 $21,371/呎
-(25年-06月-22日)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -29070,7 +29062,7 @@
           <t>F | 229呎 (开放式)
 $620万
 $27,077/呎
-(22年-05月-11日)</t>
+(22年-05月-12日)</t>
         </is>
       </c>
     </row>
@@ -29085,7 +29077,7 @@
           <t>A | 777呎 (3房)
 $2470万
 $31,794/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -29093,7 +29085,7 @@
           <t>B | 540呎 (2房)
 $1767万
 $32,725/呎
-(21年-09月-26日)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -29101,7 +29093,7 @@
           <t>C | 367呎 (1房)
 $1020万
 $27,795/呎
-(21年-09月-26日)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -29109,7 +29101,7 @@
           <t>D | 356呎 (1房)
 $982万
 $27,578/呎
-(21年-09月-26日)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -29117,7 +29109,7 @@
           <t>E | 238呎 (开放式)
 $663万
 $27,860/呎
-(22年-04月-24日)</t>
+(22年-04月-25日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -29125,7 +29117,7 @@
           <t>F | 229呎 (开放式)
 $618万
 $26,998/呎
-(21年-12月-27日)</t>
+(21年-12月-28日)</t>
         </is>
       </c>
     </row>
@@ -29148,7 +29140,7 @@
           <t>B | 540呎 (2房)
 $1757万
 $32,531/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -29156,7 +29148,7 @@
           <t>C | 367呎 (1房)
 $994万
 $27,076/呎
-(21年-09月-26日)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -29164,7 +29156,7 @@
           <t>D | 356呎 (1房)
 $937万
 $26,312/呎
-(21年-09月-26日)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -29172,7 +29164,7 @@
           <t>E | 238呎 (开放式)
 $496万
 $20,827/呎
-(25年-06月-12日)</t>
+(25年-06月-13日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -29180,7 +29172,7 @@
           <t>F | 229呎 (开放式)
 $634万
 $27,684/呎
-(21年-12月-10日)</t>
+(21年-12月-11日)</t>
         </is>
       </c>
     </row>
@@ -29195,7 +29187,7 @@
           <t>A | 777呎 (3房)
 $2449万
 $31,513/呎
-(23年-06月-13日)</t>
+(23年-06月-14日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -29203,7 +29195,7 @@
           <t>B | 540呎 (2房)
 $1733万
 $32,098/呎
-(21年-09月-26日)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -29211,7 +29203,7 @@
           <t>C | 367呎 (1房)
 $991万
 $26,996/呎
-(21年-09月-26日)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -29219,7 +29211,7 @@
           <t>D | 356呎 (1房)
 $944万
 $26,510/呎
-(21年-09月-26日)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -29227,7 +29219,7 @@
           <t>E | 238呎 (开放式)
 $494万
 $20,768/呎
-(25年-06月-12日)</t>
+(25年-06月-13日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -29235,7 +29227,7 @@
           <t>F | 229呎 (开放式)
 $619万
 $27,035/呎
-(22年-02月-08日)</t>
+(22年-02月-09日)</t>
         </is>
       </c>
     </row>
@@ -29258,7 +29250,7 @@
           <t>B | 540呎 (2房)
 $1728万
 $32,003/呎
-(22年-01月-10日)</t>
+(22年-01月-11日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -29266,7 +29258,7 @@
           <t>C | 367呎 (1房)
 $988万
 $26,918/呎
-(21年-09月-28日)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -29274,7 +29266,7 @@
           <t>D | 356呎 (1房)
 $960万
 $26,980/呎
-(21年-11月-17日)</t>
+(21年-11月-18日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -29282,7 +29274,7 @@
           <t>E | 238呎 (开放式)
 $655万
 $27,537/呎
-(22年-05月-02日)</t>
+(22年-05月-03日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -29290,7 +29282,7 @@
           <t>F | 229呎 (开放式)
 $617万
 $26,955/呎
-(22年-02月-08日)</t>
+(22年-02月-09日)</t>
         </is>
       </c>
     </row>
@@ -29313,7 +29305,7 @@
           <t>B | 540呎 (2房)
 $1740万
 $32,230/呎
-(22年-07月-31日)</t>
+(22年-08月-01日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -29321,7 +29313,7 @@
           <t>C | 367呎 (1房)
 $985万
 $26,838/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -29329,7 +29321,7 @@
           <t>D | 356呎 (1房)
 $958万
 $26,900/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -29337,7 +29329,7 @@
           <t>E | 238呎 (开放式)
 $653万
 $27,457/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -29345,7 +29337,7 @@
           <t>F | 229呎 (开放式)
 $615万
 $26,872/呎
-(22年-01月-09日)</t>
+(22年-01月-10日)</t>
         </is>
       </c>
     </row>
@@ -29376,7 +29368,7 @@
           <t>C | 367呎 (1房)
 $982万
 $26,760/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -29384,7 +29376,7 @@
           <t>D | 356呎 (1房)
 $925万
 $25,997/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -29392,7 +29384,7 @@
           <t>E | 238呎 (开放式)
 $665万
 $27,946/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -29400,7 +29392,7 @@
           <t>F | 229呎 (开放式)
 $620万
 $27,071/呎
-(22年-01月-09日)</t>
+(22年-01月-10日)</t>
         </is>
       </c>
     </row>
@@ -29423,7 +29415,7 @@
           <t>B | 540呎 (2房)
 $1748万
 $32,375/呎
-(21年-10月-14日)</t>
+(21年-10月-15日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -29431,7 +29423,7 @@
           <t>C | 367呎 (1房)
 $989万
 $26,961/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -29439,7 +29431,7 @@
           <t>D | 356呎 (1房)
 $932万
 $26,192/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -29447,7 +29439,7 @@
           <t>E | 238呎 (开放式)
 $656万
 $27,579/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -29455,7 +29447,7 @@
           <t>F | 229呎 (开放式)
 $612万
 $26,708/呎
-(22年-01月-06日)</t>
+(22年-01月-07日)</t>
         </is>
       </c>
     </row>
@@ -29486,7 +29478,7 @@
           <t>C | 367呎 (1房)
 $987万
 $26,883/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -29494,7 +29486,7 @@
           <t>D | 356呎 (1房)
 $920万
 $25,839/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -29502,7 +29494,7 @@
           <t>E | 238呎 (开放式)
 $654万
 $27,498/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -29510,7 +29502,7 @@
           <t>F | 229呎 (开放式)
 $610万
 $26,628/呎
-(22年-01月-02日)</t>
+(22年-01月-03日)</t>
         </is>
       </c>
     </row>
@@ -29525,7 +29517,7 @@
           <t>A | 777呎 (3房)
 $2405万
 $30,949/呎
-(26年-01月-15日)</t>
+(26年-01月-16日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -29533,7 +29525,7 @@
           <t>B | 540呎 (2房)
 $1720万
 $31,844/呎
-(25年-04月-07日)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -29541,7 +29533,7 @@
           <t>C | 367呎 (1房)
 $973万
 $26,522/呎
-(21年-09月-28日)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -29549,7 +29541,7 @@
           <t>D | 356呎 (1房)
 $936万
 $26,304/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -29557,7 +29549,7 @@
           <t>E | 238呎 (开放式)
 $659万
 $27,699/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -29565,7 +29557,7 @@
           <t>F | 229呎 (开放式)
 $602万
 $26,268/呎
-(22年-01月-04日)</t>
+(22年-01月-05日)</t>
         </is>
       </c>
     </row>
@@ -29596,7 +29588,7 @@
           <t>C | 367呎 (1房)
 $984万
 $26,801/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -29604,7 +29596,7 @@
           <t>D | 356呎 (1房)
 $936万
 $26,304/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -29612,7 +29604,7 @@
           <t>E | 238呎 (开放式)
 $639万
 $26,851/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -29620,7 +29612,7 @@
           <t>F | 229呎 (开放式)
 $602万
 $26,268/呎
-(21年-12月-18日)</t>
+(21年-12月-19日)</t>
         </is>
       </c>
     </row>
@@ -29635,7 +29627,7 @@
           <t>A | 777呎 (3房)
 $2398万
 $30,856/呎
-(26年-06月-16日)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -29651,7 +29643,7 @@
           <t>C | 367呎 (1房)
 $981万
 $26,723/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -29659,7 +29651,7 @@
           <t>D | 356呎 (1房)
 $943万
 $26,493/呎
-(21年-11月-16日)</t>
+(21年-11月-17日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -29667,7 +29659,7 @@
           <t>E | 238呎 (开放式)
 $657万
 $27,617/呎
-(21年-09月-03日)</t>
+(21年-09月-04日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -29675,7 +29667,7 @@
           <t>F | 229呎 (开放式)
 $600万
 $26,189/呎
-(21年-12月-28日)</t>
+(21年-12月-29日)</t>
         </is>
       </c>
     </row>
@@ -29706,7 +29698,7 @@
           <t>C | 367呎 (1房)
 $998万
 $27,197/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -29714,7 +29706,7 @@
           <t>D | 356呎 (1房)
 $940万
 $26,413/呎
-(21年-09月-03日)</t>
+(21年-09月-04日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -29722,7 +29714,7 @@
           <t>E | 238呎 (开放式)
 $649万
 $27,253/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -29730,7 +29722,7 @@
           <t>F | 229呎 (开放式)
 $598万
 $26,106/呎
-(22年-01月-02日)</t>
+(22年-01月-03日)</t>
         </is>
       </c>
     </row>
@@ -29761,7 +29753,7 @@
           <t>C | 367呎 (1房)
 $995万
 $27,117/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -29769,7 +29761,7 @@
           <t>D | 356呎 (1房)
 $937万
 $26,331/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -29777,7 +29769,7 @@
           <t>E | 238呎 (开放式)
 $653万
 $27,452/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -29785,7 +29777,7 @@
           <t>F | 229呎 (开放式)
 $609万
 $26,575/呎
-(21年-12月-29日)</t>
+(21年-12月-30日)</t>
         </is>
       </c>
     </row>
@@ -29800,7 +29792,7 @@
           <t>A | 777呎 (3房)
 $2376万
 $30,575/呎
-(25年-11月-09日)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -29816,7 +29808,7 @@
           <t>C | 367呎 (1房)
 $972万
 $26,482/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -29824,7 +29816,7 @@
           <t>D | 356呎 (1房)
 $906万
 $25,447/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -29832,7 +29824,7 @@
           <t>E | 238呎 (开放式)
 $480万
 $20,162/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="G29" s="22" t="inlineStr">
@@ -29840,7 +29832,7 @@
           <t>F | 229呎 (开放式)
 $613万
 $26,764/呎
-(21年-12月-28日)</t>
+(21年-12月-29日)</t>
         </is>
       </c>
     </row>
@@ -29871,7 +29863,7 @@
           <t>C | 367呎 (1房)
 $957万
 $26,085/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -29879,7 +29871,7 @@
           <t>D | 356呎 (1房)
 $909万
 $25,540/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -29887,7 +29879,7 @@
           <t>E | 238呎 (开放式)
 $634万
 $26,650/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="G30" s="22" t="inlineStr">
@@ -29895,7 +29887,7 @@
           <t>F | 229呎 (开放式)
 $597万
 $26,054/呎
-(21年-12月-29日)</t>
+(21年-12月-30日)</t>
         </is>
       </c>
     </row>
@@ -29926,7 +29918,7 @@
           <t>C | 367呎 (1房)
 $974万
 $26,545/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -29934,7 +29926,7 @@
           <t>D | 356呎 (1房)
 $898万
 $25,226/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -29942,7 +29934,7 @@
           <t>E | 238呎 (开放式)
 $632万
 $26,553/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="G31" s="22" t="inlineStr">
@@ -29950,7 +29942,7 @@
           <t>F | 229呎 (开放式)
 $589万
 $25,704/呎
-(22年-01月-06日)</t>
+(22年-01月-07日)</t>
         </is>
       </c>
     </row>
@@ -29981,7 +29973,7 @@
           <t>C | 367呎 (1房)
 $954万
 $26,004/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -29989,7 +29981,7 @@
           <t>D | 356呎 (1房)
 $898万
 $25,218/呎
-(21年-12月-05日)</t>
+(21年-12月-06日)</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
@@ -29997,7 +29989,7 @@
           <t>E | 238呎 (开放式)
 $625万
 $26,276/呎
-(21年-11月-25日)</t>
+(21年-11月-26日)</t>
         </is>
       </c>
       <c r="G32" s="22" t="inlineStr">
@@ -30005,7 +29997,7 @@
           <t>F | 229呎 (开放式)
 $595万
 $25,974/呎
-(22年-01月-04日)</t>
+(22年-01月-05日)</t>
         </is>
       </c>
     </row>
@@ -30036,7 +30028,7 @@
           <t>C | 367呎 (1房)
 $991万
 $27,002/呎
-(21年-11月-18日)</t>
+(21年-11月-19日)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -30044,7 +30036,7 @@
           <t>D | 356呎 (1房)
 $904万
 $25,397/呎
-(22年-01月-04日)</t>
+(22年-01月-05日)</t>
         </is>
       </c>
       <c r="F33" s="22" t="inlineStr">
@@ -30052,7 +30044,7 @@
           <t>E | 238呎 (开放式)
 $631万
 $26,505/呎
-(22年-01月-06日)</t>
+(22年-01月-07日)</t>
         </is>
       </c>
       <c r="G33" s="22" t="inlineStr">
@@ -30060,7 +30052,7 @@
           <t>F | 229呎 (开放式)
 $593万
 $25,890/呎
-(22年-01月-10日)</t>
+(22年-01月-11日)</t>
         </is>
       </c>
     </row>
@@ -30091,7 +30083,7 @@
           <t>C | 367呎 (1房)
 $988万
 $26,919/呎
-(21年-11月-18日)</t>
+(21年-11月-19日)</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
@@ -30099,7 +30091,7 @@
           <t>D | 356呎 (1房)
 $914万
 $25,681/呎
-(22年-01月-04日)</t>
+(22年-01月-05日)</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
@@ -30107,7 +30099,7 @@
           <t>E | 238呎 (开放式)
 $622万
 $26,133/呎
-(22年-03月-02日)</t>
+(22年-03月-03日)</t>
         </is>
       </c>
       <c r="G34" s="22" t="inlineStr">
@@ -30115,7 +30107,7 @@
           <t>F | 229呎 (开放式)
 $581万
 $25,380/呎
-(22年-01月-23日)</t>
+(22年-01月-24日)</t>
         </is>
       </c>
     </row>
@@ -30146,7 +30138,7 @@
           <t>C | 367呎 (1房)
 $975万
 $26,564/呎
-(22年-01月-02日)</t>
+(22年-01月-03日)</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
@@ -30154,7 +30146,7 @@
           <t>D | 356呎 (1房)
 $896万
 $25,179/呎
-(21年-11月-09日)</t>
+(21年-11月-10日)</t>
         </is>
       </c>
       <c r="F35" s="22" t="inlineStr">
@@ -30162,7 +30154,7 @@
           <t>E | 238呎 (开放式)
 $627万
 $26,327/呎
-(22年-02月-08日)</t>
+(22年-02月-09日)</t>
         </is>
       </c>
       <c r="G35" s="22" t="inlineStr">
@@ -30170,7 +30162,7 @@
           <t>F | 229呎 (开放式)
 $582万
 $25,400/呎
-(22年-01月-05日)</t>
+(22年-01月-06日)</t>
         </is>
       </c>
     </row>
@@ -30201,7 +30193,7 @@
           <t>C | 367呎 (1房)
 $738万
 $20,096/呎
-(25年-06月-22日)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="E36" s="22" t="inlineStr">
@@ -30209,7 +30201,7 @@
           <t>D | 356呎 (1房)
 $875万
 $24,583/呎
-(22年-01月-12日)</t>
+(22年-01月-13日)</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
@@ -30217,7 +30209,7 @@
           <t>E | 238呎 (开放式)
 $625万
 $26,247/呎
-(22年-07月-24日)</t>
+(22年-07月-25日)</t>
         </is>
       </c>
       <c r="G36" s="22" t="inlineStr">
@@ -30225,7 +30217,7 @@
           <t>F | 229呎 (开放式)
 $592万
 $25,848/呎
-(22年-02月-08日)</t>
+(22年-02月-09日)</t>
         </is>
       </c>
     </row>
@@ -30256,7 +30248,7 @@
           <t>C | 367呎 (1房)
 $936万
 $25,510/呎
-(21年-09月-22日)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="E37" s="22" t="inlineStr">
@@ -30264,7 +30256,7 @@
           <t>D | 356呎 (1房)
 $870万
 $24,425/呎
-(22年-03月-27日)</t>
+(22年-03月-28日)</t>
         </is>
       </c>
       <c r="F37" s="22" t="inlineStr">
@@ -30272,7 +30264,7 @@
           <t>E | 238呎 (开放式)
 $621万
 $26,085/呎
-(22年-03月-27日)</t>
+(22年-03月-28日)</t>
         </is>
       </c>
       <c r="G37" s="22" t="inlineStr">
@@ -30280,7 +30272,7 @@
           <t>F | 229呎 (开放式)
 $577万
 $25,186/呎
-(22年-02月-10日)</t>
+(22年-02月-11日)</t>
         </is>
       </c>
     </row>
@@ -30297,7 +30289,7 @@
           <t>C | 374呎 (1房)
 $739万
 $19,765/呎
-(25年-08月-12日)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="E38" s="22" t="inlineStr">
@@ -30305,7 +30297,7 @@
           <t>D | 356呎 (1房)
 $861万
 $24,188/呎
-(22年-05月-02日)</t>
+(22年-05月-03日)</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
@@ -30313,7 +30305,7 @@
           <t>E | 238呎 (开放式)
 $609万
 $25,574/呎
-(22年-08月-08日)</t>
+(22年-08月-09日)</t>
         </is>
       </c>
       <c r="G38" s="22" t="inlineStr">
@@ -30321,7 +30313,7 @@
           <t>F | 229呎 (开放式)
 $576万
 $25,139/呎
-(22年-03月-03日)</t>
+(22年-03月-04日)</t>
         </is>
       </c>
     </row>

--- a/web/files/九龙-启德-The Henley III.xlsx
+++ b/web/files/九龙-启德-The Henley III.xlsx
@@ -3064,7 +3064,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -26756,7 +26756,7 @@
           <t>A | 775呎 (3房)
 $2600万
 $33,543/呎
-(26年-07月-24日)</t>
+(26年-08月-18日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
